--- a/artfynd/A 38238-2021 artfynd.xlsx
+++ b/artfynd/A 38238-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>102326859</v>
       </c>
       <c r="B2" t="n">
-        <v>99566</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603774.0679467513</v>
+        <v>603774</v>
       </c>
       <c r="R2" t="n">
-        <v>6562868.997308684</v>
+        <v>6562869</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,19 +751,9 @@
           <t>2022-07-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-07-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
